--- a/filer/59946013_hempel.xlsx
+++ b/filer/59946013_hempel.xlsx
@@ -5327,7 +5327,9 @@
           <t>Udskudt skatteaktiv</t>
         </is>
       </c>
-      <c r="B21" s="16" t="n"/>
+      <c r="B21" s="16" t="n">
+        <v>47000</v>
+      </c>
       <c r="C21" s="16" t="n">
         <v>89000</v>
       </c>
@@ -7187,7 +7189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7292,21 +7294,25 @@
       </c>
       <c r="B4" s="37" t="inlineStr">
         <is>
-          <t>fsa:NoncurrentDeferredTaxAssets</t>
+          <t>ifrs-full:ReserveOfExchangeDifferencesOnTranslation</t>
         </is>
       </c>
       <c r="C4" s="37" t="inlineStr">
         <is>
-          <t>fsa:NoncurrentDeferredTaxAssets</t>
-        </is>
-      </c>
-      <c r="D4" s="38" t="n">
-        <v>47000</v>
-      </c>
+          <t>ifrs-full:ReserveOfExchangeDifferencesOnTranslation</t>
+        </is>
+      </c>
+      <c r="D4" s="38" t="n"/>
       <c r="E4" s="38" t="n"/>
-      <c r="F4" s="38" t="n"/>
-      <c r="G4" s="38" t="n"/>
-      <c r="H4" s="38" t="n"/>
+      <c r="F4" s="38" t="n">
+        <v>-25000</v>
+      </c>
+      <c r="G4" s="38" t="n">
+        <v>-24000</v>
+      </c>
+      <c r="H4" s="38" t="n">
+        <v>28000</v>
+      </c>
       <c r="I4" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -7321,55 +7327,22 @@
       </c>
       <c r="B5" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:ReserveOfExchangeDifferencesOnTranslation</t>
+          <t>ifrs-full:WarrantReserve</t>
         </is>
       </c>
       <c r="C5" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:ReserveOfExchangeDifferencesOnTranslation</t>
+          <t>ifrs-full:WarrantReserve</t>
         </is>
       </c>
       <c r="D5" s="35" t="n"/>
       <c r="E5" s="35" t="n"/>
-      <c r="F5" s="35" t="n">
-        <v>-25000</v>
-      </c>
-      <c r="G5" s="35" t="n">
-        <v>-24000</v>
-      </c>
+      <c r="F5" s="35" t="n"/>
+      <c r="G5" s="35" t="n"/>
       <c r="H5" s="35" t="n">
-        <v>28000</v>
+        <v>6000</v>
       </c>
       <c r="I5" s="36" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="37" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B6" s="37" t="inlineStr">
-        <is>
-          <t>ifrs-full:WarrantReserve</t>
-        </is>
-      </c>
-      <c r="C6" s="37" t="inlineStr">
-        <is>
-          <t>ifrs-full:WarrantReserve</t>
-        </is>
-      </c>
-      <c r="D6" s="38" t="n"/>
-      <c r="E6" s="38" t="n"/>
-      <c r="F6" s="38" t="n"/>
-      <c r="G6" s="38" t="n"/>
-      <c r="H6" s="38" t="n">
-        <v>6000</v>
-      </c>
-      <c r="I6" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
         </is>

--- a/filer/59946013_hempel.xlsx
+++ b/filer/59946013_hempel.xlsx
@@ -648,7 +648,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.)</t>
+          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.EUR)</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Resultatopgørelse t.kr.</t>
+          <t>Resultatopgørelse t.EUR</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -1431,7 +1431,7 @@
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>AKTIVER t.kr.</t>
+          <t>AKTIVER t.EUR</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
@@ -2765,7 +2765,7 @@
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>PASSIVER t.kr.</t>
+          <t>PASSIVER t.EUR</t>
         </is>
       </c>
       <c r="B49" s="3" t="n">
@@ -4606,7 +4606,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Resultatopgørelse &amp; nøgleoplysninger (t.kr.)</t>
+          <t>Resultatopgørelse &amp; nøgleoplysninger (t.EUR)</t>
         </is>
       </c>
       <c r="B1" s="3" t="n">
@@ -4984,7 +4984,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Balance (t.kr.)</t>
+          <t>Balance (t.EUR)</t>
         </is>
       </c>
       <c r="B1" s="3" t="n">
@@ -7038,15 +7038,15 @@
         </is>
       </c>
       <c r="B60" s="29">
-        <f>IF('balance_raw_59946013'!$F$28="","—",IF(ABS(B20-'balance_raw_59946013'!$F$28)&lt;=1,"✓ OK","❌ "&amp;TEXT(B20-'balance_raw_59946013'!$F$28,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_59946013'!$F$28="","—",IF(ABS(B20-'balance_raw_59946013'!$F$28)&lt;=1,"✓ OK","❌ "&amp;TEXT(B20-'balance_raw_59946013'!$F$28,"+#,##0;-#,##0")&amp;" t.EUR"))</f>
         <v/>
       </c>
       <c r="C60" s="29">
-        <f>IF('balance_raw_59946013'!$E$28="","—",IF(ABS(C20-'balance_raw_59946013'!$E$28)&lt;=1,"✓ OK","❌ "&amp;TEXT(C20-'balance_raw_59946013'!$E$28,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_59946013'!$E$28="","—",IF(ABS(C20-'balance_raw_59946013'!$E$28)&lt;=1,"✓ OK","❌ "&amp;TEXT(C20-'balance_raw_59946013'!$E$28,"+#,##0;-#,##0")&amp;" t.EUR"))</f>
         <v/>
       </c>
       <c r="D60" s="29">
-        <f>IF('balance_raw_59946013'!$D$28="","—",IF(ABS(D20-'balance_raw_59946013'!$D$28)&lt;=1,"✓ OK","❌ "&amp;TEXT(D20-'balance_raw_59946013'!$D$28,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_59946013'!$D$28="","—",IF(ABS(D20-'balance_raw_59946013'!$D$28)&lt;=1,"✓ OK","❌ "&amp;TEXT(D20-'balance_raw_59946013'!$D$28,"+#,##0;-#,##0")&amp;" t.EUR"))</f>
         <v/>
       </c>
       <c r="F60" s="25" t="inlineStr">
@@ -7062,15 +7062,15 @@
         </is>
       </c>
       <c r="B61" s="29">
-        <f>IF('balance_raw_59946013'!$F$56="","—",IF(ABS(B24-'balance_raw_59946013'!$F$56)&lt;=1,"✓ OK","❌ "&amp;TEXT(B24-'balance_raw_59946013'!$F$56,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_59946013'!$F$56="","—",IF(ABS(B24-'balance_raw_59946013'!$F$56)&lt;=1,"✓ OK","❌ "&amp;TEXT(B24-'balance_raw_59946013'!$F$56,"+#,##0;-#,##0")&amp;" t.EUR"))</f>
         <v/>
       </c>
       <c r="C61" s="29">
-        <f>IF('balance_raw_59946013'!$E$56="","—",IF(ABS(C24-'balance_raw_59946013'!$E$56)&lt;=1,"✓ OK","❌ "&amp;TEXT(C24-'balance_raw_59946013'!$E$56,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_59946013'!$E$56="","—",IF(ABS(C24-'balance_raw_59946013'!$E$56)&lt;=1,"✓ OK","❌ "&amp;TEXT(C24-'balance_raw_59946013'!$E$56,"+#,##0;-#,##0")&amp;" t.EUR"))</f>
         <v/>
       </c>
       <c r="D61" s="29">
-        <f>IF('balance_raw_59946013'!$D$56="","—",IF(ABS(D24-'balance_raw_59946013'!$D$56)&lt;=1,"✓ OK","❌ "&amp;TEXT(D24-'balance_raw_59946013'!$D$56,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_59946013'!$D$56="","—",IF(ABS(D24-'balance_raw_59946013'!$D$56)&lt;=1,"✓ OK","❌ "&amp;TEXT(D24-'balance_raw_59946013'!$D$56,"+#,##0;-#,##0")&amp;" t.EUR"))</f>
         <v/>
       </c>
       <c r="F61" s="25" t="inlineStr">
@@ -7086,15 +7086,15 @@
         </is>
       </c>
       <c r="B62" s="29">
-        <f>IF(ABS(B20-B24)&lt;=1,"✓ OK","❌ "&amp;TEXT(B20-B24,"+#,##0;-#,##0")&amp;" t.kr.")</f>
+        <f>IF(ABS(B20-B24)&lt;=1,"✓ OK","❌ "&amp;TEXT(B20-B24,"+#,##0;-#,##0")&amp;" t.EUR")</f>
         <v/>
       </c>
       <c r="C62" s="29">
-        <f>IF(ABS(C20-C24)&lt;=1,"✓ OK","❌ "&amp;TEXT(C20-C24,"+#,##0;-#,##0")&amp;" t.kr.")</f>
+        <f>IF(ABS(C20-C24)&lt;=1,"✓ OK","❌ "&amp;TEXT(C20-C24,"+#,##0;-#,##0")&amp;" t.EUR")</f>
         <v/>
       </c>
       <c r="D62" s="29">
-        <f>IF(ABS(D20-D24)&lt;=1,"✓ OK","❌ "&amp;TEXT(D20-D24,"+#,##0;-#,##0")&amp;" t.kr.")</f>
+        <f>IF(ABS(D20-D24)&lt;=1,"✓ OK","❌ "&amp;TEXT(D20-D24,"+#,##0;-#,##0")&amp;" t.EUR")</f>
         <v/>
       </c>
       <c r="F62" s="25" t="inlineStr">
@@ -7110,15 +7110,15 @@
         </is>
       </c>
       <c r="B63" s="29">
-        <f>IF('res_raw_59946013'!$F$4="","—",IF(ABS(B7-'res_raw_59946013'!$F$4)&lt;=1,"✓ OK","❌ "&amp;TEXT(B7-'res_raw_59946013'!$F$4,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw_59946013'!$F$4="","—",IF(ABS(B7-'res_raw_59946013'!$F$4)&lt;=1,"✓ OK","❌ "&amp;TEXT(B7-'res_raw_59946013'!$F$4,"+#,##0;-#,##0")&amp;" t.EUR"))</f>
         <v/>
       </c>
       <c r="C63" s="29">
-        <f>IF('res_raw_59946013'!$E$4="","—",IF(ABS(C7-'res_raw_59946013'!$E$4)&lt;=1,"✓ OK","❌ "&amp;TEXT(C7-'res_raw_59946013'!$E$4,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw_59946013'!$E$4="","—",IF(ABS(C7-'res_raw_59946013'!$E$4)&lt;=1,"✓ OK","❌ "&amp;TEXT(C7-'res_raw_59946013'!$E$4,"+#,##0;-#,##0")&amp;" t.EUR"))</f>
         <v/>
       </c>
       <c r="D63" s="29">
-        <f>IF('res_raw_59946013'!$D$4="","—",IF(ABS(D7-'res_raw_59946013'!$D$4)&lt;=1,"✓ OK","❌ "&amp;TEXT(D7-'res_raw_59946013'!$D$4,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw_59946013'!$D$4="","—",IF(ABS(D7-'res_raw_59946013'!$D$4)&lt;=1,"✓ OK","❌ "&amp;TEXT(D7-'res_raw_59946013'!$D$4,"+#,##0;-#,##0")&amp;" t.EUR"))</f>
         <v/>
       </c>
       <c r="F63" s="25" t="inlineStr">
@@ -7134,15 +7134,15 @@
         </is>
       </c>
       <c r="B64" s="29">
-        <f>IF('res_raw_59946013'!$F$9="","—",IF(ABS(B12-'res_raw_59946013'!$F$9)&lt;=1,"✓ OK","❌ "&amp;TEXT(B12-'res_raw_59946013'!$F$9,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw_59946013'!$F$9="","—",IF(ABS(B12-'res_raw_59946013'!$F$9)&lt;=1,"✓ OK","❌ "&amp;TEXT(B12-'res_raw_59946013'!$F$9,"+#,##0;-#,##0")&amp;" t.EUR"))</f>
         <v/>
       </c>
       <c r="C64" s="29">
-        <f>IF('res_raw_59946013'!$E$9="","—",IF(ABS(C12-'res_raw_59946013'!$E$9)&lt;=1,"✓ OK","❌ "&amp;TEXT(C12-'res_raw_59946013'!$E$9,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw_59946013'!$E$9="","—",IF(ABS(C12-'res_raw_59946013'!$E$9)&lt;=1,"✓ OK","❌ "&amp;TEXT(C12-'res_raw_59946013'!$E$9,"+#,##0;-#,##0")&amp;" t.EUR"))</f>
         <v/>
       </c>
       <c r="D64" s="29">
-        <f>IF('res_raw_59946013'!$D$9="","—",IF(ABS(D12-'res_raw_59946013'!$D$9)&lt;=1,"✓ OK","❌ "&amp;TEXT(D12-'res_raw_59946013'!$D$9,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw_59946013'!$D$9="","—",IF(ABS(D12-'res_raw_59946013'!$D$9)&lt;=1,"✓ OK","❌ "&amp;TEXT(D12-'res_raw_59946013'!$D$9,"+#,##0;-#,##0")&amp;" t.EUR"))</f>
         <v/>
       </c>
       <c r="F64" s="25" t="inlineStr">
@@ -7158,15 +7158,15 @@
         </is>
       </c>
       <c r="B65" s="29">
-        <f>IF('res_raw_59946013'!$F$14="","—",IF(ABS(B15-'res_raw_59946013'!$F$14)&lt;=1,"✓ OK","❌ "&amp;TEXT(B15-'res_raw_59946013'!$F$14,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw_59946013'!$F$14="","—",IF(ABS(B15-'res_raw_59946013'!$F$14)&lt;=1,"✓ OK","❌ "&amp;TEXT(B15-'res_raw_59946013'!$F$14,"+#,##0;-#,##0")&amp;" t.EUR"))</f>
         <v/>
       </c>
       <c r="C65" s="29">
-        <f>IF('res_raw_59946013'!$E$14="","—",IF(ABS(C15-'res_raw_59946013'!$E$14)&lt;=1,"✓ OK","❌ "&amp;TEXT(C15-'res_raw_59946013'!$E$14,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw_59946013'!$E$14="","—",IF(ABS(C15-'res_raw_59946013'!$E$14)&lt;=1,"✓ OK","❌ "&amp;TEXT(C15-'res_raw_59946013'!$E$14,"+#,##0;-#,##0")&amp;" t.EUR"))</f>
         <v/>
       </c>
       <c r="D65" s="29">
-        <f>IF('res_raw_59946013'!$D$14="","—",IF(ABS(D15-'res_raw_59946013'!$D$14)&lt;=1,"✓ OK","❌ "&amp;TEXT(D15-'res_raw_59946013'!$D$14,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw_59946013'!$D$14="","—",IF(ABS(D15-'res_raw_59946013'!$D$14)&lt;=1,"✓ OK","❌ "&amp;TEXT(D15-'res_raw_59946013'!$D$14,"+#,##0;-#,##0")&amp;" t.EUR"))</f>
         <v/>
       </c>
       <c r="F65" s="25" t="inlineStr">

--- a/filer/59946013_hempel.xlsx
+++ b/filer/59946013_hempel.xlsx
@@ -648,7 +648,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.EUR)</t>
+          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.EUR) · Klasse C-stor · Revision</t>
         </is>
       </c>
     </row>

--- a/filer/59946013_hempel.xlsx
+++ b/filer/59946013_hempel.xlsx
@@ -10,8 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overblik_59946013" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="res_raw_59946013" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="balance_raw_59946013" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_funktion" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Noter_info" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pengestrom_raw_59946013" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_funktion" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Noter_info" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -204,9 +205,9 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -628,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L94"/>
+  <dimension ref="A1:L101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -4578,6 +4579,148 @@
       </c>
       <c r="F94" s="13">
         <f>IFERROR($F$34/($F$56+$F$63)*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="15" t="inlineStr">
+        <is>
+          <t>PENGESTRØMSOPGØRELSE t.EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B97" s="17">
+        <f>'pengestrom_raw_59946013'!$B$2</f>
+        <v/>
+      </c>
+      <c r="C97" s="17">
+        <f>'pengestrom_raw_59946013'!$C$2</f>
+        <v/>
+      </c>
+      <c r="D97" s="17">
+        <f>'pengestrom_raw_59946013'!$D$2</f>
+        <v/>
+      </c>
+      <c r="E97" s="17">
+        <f>'pengestrom_raw_59946013'!$E$2</f>
+        <v/>
+      </c>
+      <c r="F97" s="17">
+        <f>'pengestrom_raw_59946013'!$F$2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B98" s="17">
+        <f>'pengestrom_raw_59946013'!$B$3</f>
+        <v/>
+      </c>
+      <c r="C98" s="17">
+        <f>'pengestrom_raw_59946013'!$C$3</f>
+        <v/>
+      </c>
+      <c r="D98" s="17">
+        <f>'pengestrom_raw_59946013'!$D$3</f>
+        <v/>
+      </c>
+      <c r="E98" s="17">
+        <f>'pengestrom_raw_59946013'!$E$3</f>
+        <v/>
+      </c>
+      <c r="F98" s="17">
+        <f>'pengestrom_raw_59946013'!$F$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B99" s="17">
+        <f>'pengestrom_raw_59946013'!$B$4</f>
+        <v/>
+      </c>
+      <c r="C99" s="17">
+        <f>'pengestrom_raw_59946013'!$C$4</f>
+        <v/>
+      </c>
+      <c r="D99" s="17">
+        <f>'pengestrom_raw_59946013'!$D$4</f>
+        <v/>
+      </c>
+      <c r="E99" s="17">
+        <f>'pengestrom_raw_59946013'!$E$4</f>
+        <v/>
+      </c>
+      <c r="F99" s="17">
+        <f>'pengestrom_raw_59946013'!$F$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm (rapporteret)</t>
+        </is>
+      </c>
+      <c r="B100" s="17">
+        <f>'pengestrom_raw_59946013'!$B$5</f>
+        <v/>
+      </c>
+      <c r="C100" s="17">
+        <f>'pengestrom_raw_59946013'!$C$5</f>
+        <v/>
+      </c>
+      <c r="D100" s="17">
+        <f>'pengestrom_raw_59946013'!$D$5</f>
+        <v/>
+      </c>
+      <c r="E100" s="17">
+        <f>'pengestrom_raw_59946013'!$E$5</f>
+        <v/>
+      </c>
+      <c r="F100" s="17">
+        <f>'pengestrom_raw_59946013'!$F$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="16" t="inlineStr">
+        <is>
+          <t>Krydstjek: drift + inv. + fin. = årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B101">
+        <f>IF(ABS(('pengestrom_raw_59946013'!$B$2+'pengestrom_raw_59946013'!$B$3+'pengestrom_raw_59946013'!$B$4)-'pengestrom_raw_59946013'!$B$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_59946013'!$B$2+'pengestrom_raw_59946013'!$B$3+'pengestrom_raw_59946013'!$B$4)-'pengestrom_raw_59946013'!$B$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="C101">
+        <f>IF(ABS(('pengestrom_raw_59946013'!$C$2+'pengestrom_raw_59946013'!$C$3+'pengestrom_raw_59946013'!$C$4)-'pengestrom_raw_59946013'!$C$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_59946013'!$C$2+'pengestrom_raw_59946013'!$C$3+'pengestrom_raw_59946013'!$C$4)-'pengestrom_raw_59946013'!$C$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="D101">
+        <f>IF(ABS(('pengestrom_raw_59946013'!$D$2+'pengestrom_raw_59946013'!$D$3+'pengestrom_raw_59946013'!$D$4)-'pengestrom_raw_59946013'!$D$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_59946013'!$D$2+'pengestrom_raw_59946013'!$D$3+'pengestrom_raw_59946013'!$D$4)-'pengestrom_raw_59946013'!$D$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="E101">
+        <f>IF(ABS(('pengestrom_raw_59946013'!$E$2+'pengestrom_raw_59946013'!$E$3+'pengestrom_raw_59946013'!$E$4)-'pengestrom_raw_59946013'!$E$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_59946013'!$E$2+'pengestrom_raw_59946013'!$E$3+'pengestrom_raw_59946013'!$E$4)-'pengestrom_raw_59946013'!$E$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="F101">
+        <f>IF(ABS(('pengestrom_raw_59946013'!$F$2+'pengestrom_raw_59946013'!$F$3+'pengestrom_raw_59946013'!$F$4)-'pengestrom_raw_59946013'!$F$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_59946013'!$F$2+'pengestrom_raw_59946013'!$F$3+'pengestrom_raw_59946013'!$F$4)-'pengestrom_raw_59946013'!$F$5,"+#,##0;-#,##0"))</f>
         <v/>
       </c>
     </row>
@@ -4626,336 +4769,336 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Nettoomsætning</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n">
+      <c r="B2" s="17" t="n">
         <v>1542000</v>
       </c>
-      <c r="C2" s="16" t="n">
+      <c r="C2" s="17" t="n">
         <v>1774000</v>
       </c>
-      <c r="D2" s="16" t="n">
+      <c r="D2" s="17" t="n">
         <v>2159000</v>
       </c>
-      <c r="E2" s="16" t="n">
+      <c r="E2" s="17" t="n">
         <v>2351000</v>
       </c>
-      <c r="F2" s="16" t="n">
+      <c r="F2" s="17" t="n">
         <v>2185000</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Produktionsomkostninger</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n">
+      <c r="B3" s="17" t="n">
         <v>937000</v>
       </c>
-      <c r="C3" s="16" t="n"/>
-      <c r="D3" s="16" t="n">
+      <c r="C3" s="17" t="n"/>
+      <c r="D3" s="17" t="n">
         <v>1375000</v>
       </c>
-      <c r="E3" s="16" t="n">
+      <c r="E3" s="17" t="n">
         <v>1436000</v>
       </c>
-      <c r="F3" s="16" t="n">
+      <c r="F3" s="17" t="n">
         <v>1237000</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>Bruttoresultat</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
+      <c r="B4" s="17" t="n">
         <v>605000</v>
       </c>
-      <c r="C4" s="16" t="n">
+      <c r="C4" s="17" t="n">
         <v>672000</v>
       </c>
-      <c r="D4" s="16" t="n">
+      <c r="D4" s="17" t="n">
         <v>784000</v>
       </c>
-      <c r="E4" s="16" t="n">
+      <c r="E4" s="17" t="n">
         <v>915000</v>
       </c>
-      <c r="F4" s="16" t="n">
+      <c r="F4" s="17" t="n">
         <v>948000</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Salgs- og distributionsomkostninger</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <v>397000</v>
       </c>
-      <c r="C5" s="16" t="n"/>
-      <c r="D5" s="16" t="n">
+      <c r="C5" s="17" t="n"/>
+      <c r="D5" s="17" t="n">
         <v>552000</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="E5" s="17" t="n">
         <v>561000</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="F5" s="17" t="n">
         <v>511000</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Administrationsomkostninger</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="17" t="n">
         <v>120000</v>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="17" t="n">
         <v>121000</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="D6" s="17" t="n">
         <v>121000</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="E6" s="17" t="n">
         <v>165000</v>
       </c>
-      <c r="F6" s="16" t="n">
+      <c r="F6" s="17" t="n">
         <v>160000</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Andre driftsindtægter</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="17" t="n">
         <v>1000</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="17" t="n">
         <v>20000</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="D7" s="17" t="n">
         <v>4000</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="16" t="n"/>
+      <c r="F7" s="17" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Andre driftsomkostninger</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n"/>
-      <c r="C8" s="16" t="n">
+      <c r="B8" s="17" t="n"/>
+      <c r="C8" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="16" t="n"/>
-      <c r="E8" s="16" t="n"/>
-      <c r="F8" s="16" t="n"/>
+      <c r="D8" s="17" t="n"/>
+      <c r="E8" s="17" t="n"/>
+      <c r="F8" s="17" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>Resultat af primær drift</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="17" t="n">
         <v>89000</v>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="17" t="n">
         <v>112000</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="D9" s="17" t="n">
         <v>114000</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="E9" s="17" t="n">
         <v>189000</v>
       </c>
-      <c r="F9" s="16" t="n"/>
+      <c r="F9" s="17" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Indtægter af kapitalandele, dattervirksomheder</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="C10" s="16" t="n"/>
-      <c r="D10" s="16" t="n"/>
-      <c r="E10" s="16" t="n"/>
-      <c r="F10" s="16" t="n"/>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="17" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Finansielle indtægter</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n"/>
-      <c r="C11" s="16" t="n">
+      <c r="B11" s="17" t="n"/>
+      <c r="C11" s="17" t="n">
         <v>4000</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>12000</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>14000</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="F11" s="17" t="n">
         <v>39000</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Finansielle omkostninger</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="17" t="n">
         <v>25000</v>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="17" t="n">
         <v>21000</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="17" t="n">
         <v>70000</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="17" t="n">
         <v>121000</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="F12" s="17" t="n">
         <v>96000</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>Finansielle poster, netto</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
+      <c r="B13" s="17" t="n">
         <v>-25000</v>
       </c>
-      <c r="C13" s="16" t="n"/>
-      <c r="D13" s="16" t="n"/>
-      <c r="E13" s="16" t="n"/>
-      <c r="F13" s="16" t="n"/>
+      <c r="C13" s="17" t="n"/>
+      <c r="D13" s="17" t="n"/>
+      <c r="E13" s="17" t="n"/>
+      <c r="F13" s="17" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>Resultat før skat</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
+      <c r="B14" s="17" t="n">
         <v>64000</v>
       </c>
-      <c r="C14" s="16" t="n">
+      <c r="C14" s="17" t="n">
         <v>95000</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="17" t="n">
         <v>56000</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="E14" s="17" t="n">
         <v>82000</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="F14" s="17" t="n">
         <v>220000</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Skat af årets resultat</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
+      <c r="B15" s="17" t="n">
         <v>21000</v>
       </c>
-      <c r="C15" s="16" t="n">
+      <c r="C15" s="17" t="n">
         <v>29000</v>
       </c>
-      <c r="D15" s="16" t="n">
+      <c r="D15" s="17" t="n">
         <v>19000</v>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="E15" s="17" t="n">
         <v>21000</v>
       </c>
-      <c r="F15" s="16" t="n">
+      <c r="F15" s="17" t="n">
         <v>50000</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Årets resultat</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
+      <c r="B16" s="17" t="n">
         <v>43000</v>
       </c>
-      <c r="C16" s="16" t="n">
+      <c r="C16" s="17" t="n">
         <v>66000</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="D16" s="17" t="n">
         <v>37000</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="E16" s="17" t="n">
         <v>61000</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="F16" s="17" t="n">
         <v>170000</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Gns. antal medarbejdere</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n">
+      <c r="B17" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="C17" s="16" t="n">
+      <c r="C17" s="17" t="n">
         <v>6746</v>
       </c>
-      <c r="D17" s="16" t="n"/>
-      <c r="E17" s="16" t="n"/>
-      <c r="F17" s="16" t="n"/>
+      <c r="D17" s="17" t="n"/>
+      <c r="E17" s="17" t="n"/>
+      <c r="F17" s="17" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Investering i materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
+      <c r="B18" s="17" t="n">
         <v>62000</v>
       </c>
-      <c r="C18" s="16" t="n">
+      <c r="C18" s="17" t="n">
         <v>86000</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="D18" s="17" t="n">
         <v>84000</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="E18" s="17" t="n">
         <v>71000</v>
       </c>
-      <c r="F18" s="16" t="n">
+      <c r="F18" s="17" t="n">
         <v>61000</v>
       </c>
     </row>
@@ -5004,978 +5147,978 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Udviklingsprojekter</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n">
+      <c r="B2" s="17" t="n">
         <v>4000</v>
       </c>
-      <c r="C2" s="16" t="n"/>
-      <c r="D2" s="16" t="n"/>
-      <c r="E2" s="16" t="n"/>
-      <c r="F2" s="16" t="n"/>
+      <c r="C2" s="17" t="n"/>
+      <c r="D2" s="17" t="n"/>
+      <c r="E2" s="17" t="n"/>
+      <c r="F2" s="17" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Patenter, varemærker mv.</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n"/>
-      <c r="C3" s="16" t="n"/>
-      <c r="D3" s="16" t="n"/>
-      <c r="E3" s="16" t="n"/>
-      <c r="F3" s="16" t="n"/>
+      <c r="B3" s="17" t="n"/>
+      <c r="C3" s="17" t="n"/>
+      <c r="D3" s="17" t="n"/>
+      <c r="E3" s="17" t="n"/>
+      <c r="F3" s="17" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Goodwill</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
+      <c r="B4" s="17" t="n">
         <v>56000</v>
       </c>
-      <c r="C4" s="16" t="n"/>
-      <c r="D4" s="16" t="n"/>
-      <c r="E4" s="16" t="n"/>
-      <c r="F4" s="16" t="n"/>
+      <c r="C4" s="17" t="n"/>
+      <c r="D4" s="17" t="n"/>
+      <c r="E4" s="17" t="n"/>
+      <c r="F4" s="17" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>Immaterielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <v>142000</v>
       </c>
-      <c r="C5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <v>767000</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <v>765000</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="E5" s="17" t="n">
         <v>761000</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="F5" s="17" t="n">
         <v>793000</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Grunde og bygninger</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="17" t="n">
         <v>154000</v>
       </c>
-      <c r="C6" s="16" t="n"/>
-      <c r="D6" s="16" t="n"/>
-      <c r="E6" s="16" t="n"/>
-      <c r="F6" s="16" t="n"/>
+      <c r="C6" s="17" t="n"/>
+      <c r="D6" s="17" t="n"/>
+      <c r="E6" s="17" t="n"/>
+      <c r="F6" s="17" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Produktionsanlæg og maskiner</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="17" t="n">
         <v>81000</v>
       </c>
-      <c r="C7" s="16" t="n"/>
-      <c r="D7" s="16" t="n"/>
-      <c r="E7" s="16" t="n"/>
-      <c r="F7" s="16" t="n"/>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="17" t="n"/>
+      <c r="F7" s="17" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Driftsmateriel og inventar</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="17" t="n">
         <v>29000</v>
       </c>
-      <c r="C8" s="16" t="n"/>
-      <c r="D8" s="16" t="n"/>
-      <c r="E8" s="16" t="n"/>
-      <c r="F8" s="16" t="n"/>
+      <c r="C8" s="17" t="n"/>
+      <c r="D8" s="17" t="n"/>
+      <c r="E8" s="17" t="n"/>
+      <c r="F8" s="17" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Indretning af lejede lokaler</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n"/>
-      <c r="C9" s="16" t="n"/>
-      <c r="D9" s="16" t="n"/>
-      <c r="E9" s="16" t="n"/>
-      <c r="F9" s="16" t="n"/>
+      <c r="B9" s="17" t="n"/>
+      <c r="C9" s="17" t="n"/>
+      <c r="D9" s="17" t="n"/>
+      <c r="E9" s="17" t="n"/>
+      <c r="F9" s="17" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Forudbetaling og anlægsaktiver under opførelse</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="17" t="n">
         <v>74000</v>
       </c>
-      <c r="C10" s="16" t="n"/>
-      <c r="D10" s="16" t="n"/>
-      <c r="E10" s="16" t="n"/>
-      <c r="F10" s="16" t="n"/>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="17" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <v>338000</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <v>477000</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>511000</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>492000</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="F11" s="17" t="n">
         <v>480000</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Kapitalandele, dattervirksomheder</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="C12" s="16" t="n"/>
-      <c r="D12" s="16" t="n"/>
-      <c r="E12" s="16" t="n"/>
-      <c r="F12" s="16" t="n"/>
+      <c r="C12" s="17" t="n"/>
+      <c r="D12" s="17" t="n"/>
+      <c r="E12" s="17" t="n"/>
+      <c r="F12" s="17" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Deposita</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
+      <c r="B13" s="17" t="n">
         <v>4000</v>
       </c>
-      <c r="C13" s="16" t="n">
+      <c r="C13" s="17" t="n">
         <v>11000</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="17" t="n">
         <v>13000</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="E13" s="17" t="n">
         <v>13000</v>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="F13" s="17" t="n">
         <v>9000</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>Finansielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
+      <c r="B14" s="17" t="n">
         <v>51000</v>
       </c>
-      <c r="C14" s="16" t="n"/>
-      <c r="D14" s="16" t="n"/>
-      <c r="E14" s="16" t="n"/>
-      <c r="F14" s="16" t="n"/>
+      <c r="C14" s="17" t="n"/>
+      <c r="D14" s="17" t="n"/>
+      <c r="E14" s="17" t="n"/>
+      <c r="F14" s="17" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>Anlægsaktiver</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
+      <c r="B15" s="17" t="n">
         <v>531000</v>
       </c>
-      <c r="C15" s="16" t="n">
+      <c r="C15" s="17" t="n">
         <v>1516000</v>
       </c>
-      <c r="D15" s="16" t="n">
+      <c r="D15" s="17" t="n">
         <v>1544000</v>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="E15" s="17" t="n">
         <v>1514000</v>
       </c>
-      <c r="F15" s="16" t="n">
+      <c r="F15" s="17" t="n">
         <v>1530000</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Varebeholdninger</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
+      <c r="B16" s="17" t="n">
         <v>220000</v>
       </c>
-      <c r="C16" s="16" t="n">
+      <c r="C16" s="17" t="n">
         <v>334000</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="D16" s="17" t="n">
         <v>343000</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="E16" s="17" t="n">
         <v>332000</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="F16" s="17" t="n">
         <v>336000</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavender fra salg og tjenesteydelser</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n">
+      <c r="B17" s="17" t="n">
         <v>335000</v>
       </c>
-      <c r="C17" s="16" t="n">
+      <c r="C17" s="17" t="n">
         <v>397000</v>
       </c>
-      <c r="D17" s="16" t="n">
+      <c r="D17" s="17" t="n">
         <v>476000</v>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="E17" s="17" t="n">
         <v>505000</v>
       </c>
-      <c r="F17" s="16" t="n">
+      <c r="F17" s="17" t="n">
         <v>450000</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavender hos tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
+      <c r="B18" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="C18" s="16" t="n"/>
-      <c r="D18" s="16" t="n"/>
-      <c r="E18" s="16" t="n"/>
-      <c r="F18" s="16" t="n"/>
+      <c r="C18" s="17" t="n"/>
+      <c r="D18" s="17" t="n"/>
+      <c r="E18" s="17" t="n"/>
+      <c r="F18" s="17" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Andre tilgodehavender</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n">
+      <c r="B19" s="17" t="n">
         <v>41000</v>
       </c>
-      <c r="C19" s="16" t="n"/>
-      <c r="D19" s="16" t="n"/>
-      <c r="E19" s="16" t="n"/>
-      <c r="F19" s="16" t="n"/>
+      <c r="C19" s="17" t="n"/>
+      <c r="D19" s="17" t="n"/>
+      <c r="E19" s="17" t="n"/>
+      <c r="F19" s="17" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Periodeafgrænsningsposter (aktiver)</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n">
+      <c r="B20" s="17" t="n">
         <v>15000</v>
       </c>
-      <c r="C20" s="16" t="n">
+      <c r="C20" s="17" t="n">
         <v>21000</v>
       </c>
-      <c r="D20" s="16" t="n">
+      <c r="D20" s="17" t="n">
         <v>17000</v>
       </c>
-      <c r="E20" s="16" t="n">
+      <c r="E20" s="17" t="n">
         <v>18000</v>
       </c>
-      <c r="F20" s="16" t="n">
+      <c r="F20" s="17" t="n">
         <v>20000</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>Udskudt skatteaktiv</t>
         </is>
       </c>
-      <c r="B21" s="16" t="n">
+      <c r="B21" s="17" t="n">
         <v>47000</v>
       </c>
-      <c r="C21" s="16" t="n">
+      <c r="C21" s="17" t="n">
         <v>89000</v>
       </c>
-      <c r="D21" s="16" t="n">
+      <c r="D21" s="17" t="n">
         <v>94000</v>
       </c>
-      <c r="E21" s="16" t="n">
+      <c r="E21" s="17" t="n">
         <v>112000</v>
       </c>
-      <c r="F21" s="16" t="n">
+      <c r="F21" s="17" t="n">
         <v>122000</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B22" s="16" t="n"/>
-      <c r="C22" s="16" t="n"/>
-      <c r="D22" s="16" t="n"/>
-      <c r="E22" s="16" t="n"/>
-      <c r="F22" s="16" t="n"/>
+      <c r="B22" s="17" t="n"/>
+      <c r="C22" s="17" t="n"/>
+      <c r="D22" s="17" t="n"/>
+      <c r="E22" s="17" t="n"/>
+      <c r="F22" s="17" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>Kortfristede skattetilgodehavender</t>
         </is>
       </c>
-      <c r="B23" s="16" t="n">
+      <c r="B23" s="17" t="n">
         <v>3000</v>
       </c>
-      <c r="C23" s="16" t="n">
+      <c r="C23" s="17" t="n">
         <v>4000</v>
       </c>
-      <c r="D23" s="16" t="n">
+      <c r="D23" s="17" t="n">
         <v>4000</v>
       </c>
-      <c r="E23" s="16" t="n">
+      <c r="E23" s="17" t="n">
         <v>18000</v>
       </c>
-      <c r="F23" s="16" t="n">
+      <c r="F23" s="17" t="n">
         <v>22000</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="17" t="inlineStr">
+      <c r="A24" s="15" t="inlineStr">
         <is>
           <t>Tilgodehavender</t>
         </is>
       </c>
-      <c r="B24" s="16" t="n">
+      <c r="B24" s="17" t="n">
         <v>394000</v>
       </c>
-      <c r="C24" s="16" t="n">
+      <c r="C24" s="17" t="n">
         <v>48000</v>
       </c>
-      <c r="D24" s="16" t="n">
+      <c r="D24" s="17" t="n">
         <v>70000</v>
       </c>
-      <c r="E24" s="16" t="n">
+      <c r="E24" s="17" t="n">
         <v>71000</v>
       </c>
-      <c r="F24" s="16" t="n">
+      <c r="F24" s="17" t="n">
         <v>63000</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>Værdipapirer</t>
         </is>
       </c>
-      <c r="B25" s="16" t="n"/>
-      <c r="C25" s="16" t="n"/>
-      <c r="D25" s="16" t="n"/>
-      <c r="E25" s="16" t="n"/>
-      <c r="F25" s="16" t="n"/>
+      <c r="B25" s="17" t="n"/>
+      <c r="C25" s="17" t="n"/>
+      <c r="D25" s="17" t="n"/>
+      <c r="E25" s="17" t="n"/>
+      <c r="F25" s="17" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="inlineStr">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>Likvide beholdninger</t>
         </is>
       </c>
-      <c r="B26" s="16" t="n">
+      <c r="B26" s="17" t="n">
         <v>265000</v>
       </c>
-      <c r="C26" s="16" t="n">
+      <c r="C26" s="17" t="n">
         <v>176000</v>
       </c>
-      <c r="D26" s="16" t="n">
+      <c r="D26" s="17" t="n">
         <v>180000</v>
       </c>
-      <c r="E26" s="16" t="n">
+      <c r="E26" s="17" t="n">
         <v>209000</v>
       </c>
-      <c r="F26" s="16" t="n">
+      <c r="F26" s="17" t="n">
         <v>210000</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="17" t="inlineStr">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>Omsætningsaktiver</t>
         </is>
       </c>
-      <c r="B27" s="16" t="n">
+      <c r="B27" s="17" t="n">
         <v>879000</v>
       </c>
-      <c r="C27" s="16" t="n">
+      <c r="C27" s="17" t="n">
         <v>980000</v>
       </c>
-      <c r="D27" s="16" t="n">
+      <c r="D27" s="17" t="n">
         <v>1111000</v>
       </c>
-      <c r="E27" s="16" t="n">
+      <c r="E27" s="17" t="n">
         <v>1153000</v>
       </c>
-      <c r="F27" s="16" t="n">
+      <c r="F27" s="17" t="n">
         <v>1101000</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="17" t="inlineStr">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>Aktiver</t>
         </is>
       </c>
-      <c r="B28" s="16" t="n">
+      <c r="B28" s="17" t="n">
         <v>1410000</v>
       </c>
-      <c r="C28" s="16" t="n">
+      <c r="C28" s="17" t="n">
         <v>2496000</v>
       </c>
-      <c r="D28" s="16" t="n">
+      <c r="D28" s="17" t="n">
         <v>2655000</v>
       </c>
-      <c r="E28" s="16" t="n">
+      <c r="E28" s="17" t="n">
         <v>2667000</v>
       </c>
-      <c r="F28" s="16" t="n">
+      <c r="F28" s="17" t="n">
         <v>2631000</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>Selskabskapital</t>
         </is>
       </c>
-      <c r="B29" s="16" t="n">
+      <c r="B29" s="17" t="n">
         <v>15000</v>
       </c>
-      <c r="C29" s="16" t="n">
+      <c r="C29" s="17" t="n">
         <v>15000</v>
       </c>
-      <c r="D29" s="16" t="n">
+      <c r="D29" s="17" t="n">
         <v>15000</v>
       </c>
-      <c r="E29" s="16" t="n">
+      <c r="E29" s="17" t="n">
         <v>15000</v>
       </c>
-      <c r="F29" s="16" t="n">
+      <c r="F29" s="17" t="n">
         <v>19000</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="15" t="inlineStr">
+      <c r="A30" s="16" t="inlineStr">
         <is>
           <t>Reserve for nettoopskrivning (indre værdis metode)</t>
         </is>
       </c>
-      <c r="B30" s="16" t="n"/>
-      <c r="C30" s="16" t="n"/>
-      <c r="D30" s="16" t="n"/>
-      <c r="E30" s="16" t="n"/>
-      <c r="F30" s="16" t="n"/>
+      <c r="B30" s="17" t="n"/>
+      <c r="C30" s="17" t="n"/>
+      <c r="D30" s="17" t="n"/>
+      <c r="E30" s="17" t="n"/>
+      <c r="F30" s="17" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="15" t="inlineStr">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t>Reserve for udviklingsomkostninger</t>
         </is>
       </c>
-      <c r="B31" s="16" t="n">
+      <c r="B31" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="C31" s="16" t="n"/>
-      <c r="D31" s="16" t="n"/>
-      <c r="E31" s="16" t="n"/>
-      <c r="F31" s="16" t="n"/>
+      <c r="C31" s="17" t="n"/>
+      <c r="D31" s="17" t="n"/>
+      <c r="E31" s="17" t="n"/>
+      <c r="F31" s="17" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="15" t="inlineStr">
+      <c r="A32" s="16" t="inlineStr">
         <is>
           <t>Reserve for sikringstransaktioner</t>
         </is>
       </c>
-      <c r="B32" s="16" t="n"/>
-      <c r="C32" s="16" t="n"/>
-      <c r="D32" s="16" t="n"/>
-      <c r="E32" s="16" t="n"/>
-      <c r="F32" s="16" t="n"/>
+      <c r="B32" s="17" t="n"/>
+      <c r="C32" s="17" t="n"/>
+      <c r="D32" s="17" t="n"/>
+      <c r="E32" s="17" t="n"/>
+      <c r="F32" s="17" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="15" t="inlineStr">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>Andre reserver</t>
         </is>
       </c>
-      <c r="B33" s="16" t="n">
+      <c r="B33" s="17" t="n">
         <v>-33000</v>
       </c>
-      <c r="C33" s="16" t="n"/>
-      <c r="D33" s="16" t="n">
+      <c r="C33" s="17" t="n"/>
+      <c r="D33" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E33" s="16" t="n">
+      <c r="E33" s="17" t="n">
         <v>-4000</v>
       </c>
-      <c r="F33" s="16" t="n">
+      <c r="F33" s="17" t="n">
         <v>590000</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="15" t="inlineStr">
+      <c r="A34" s="16" t="inlineStr">
         <is>
           <t>Overført resultat</t>
         </is>
       </c>
-      <c r="B34" s="16" t="n">
+      <c r="B34" s="17" t="n">
         <v>436000</v>
       </c>
-      <c r="C34" s="16" t="n">
+      <c r="C34" s="17" t="n">
         <v>482000</v>
       </c>
-      <c r="D34" s="16" t="n">
+      <c r="D34" s="17" t="n">
         <v>529000</v>
       </c>
-      <c r="E34" s="16" t="n">
+      <c r="E34" s="17" t="n">
         <v>490000</v>
       </c>
-      <c r="F34" s="16" t="n">
+      <c r="F34" s="17" t="n">
         <v>417000</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="17" t="inlineStr">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>Egenkapital i alt</t>
         </is>
       </c>
-      <c r="B35" s="16" t="n">
+      <c r="B35" s="17" t="n">
         <v>486000</v>
       </c>
-      <c r="C35" s="16" t="n">
+      <c r="C35" s="17" t="n">
         <v>529000</v>
       </c>
-      <c r="D35" s="16" t="n">
+      <c r="D35" s="17" t="n">
         <v>519000</v>
       </c>
-      <c r="E35" s="16" t="n">
+      <c r="E35" s="17" t="n">
         <v>502000</v>
       </c>
-      <c r="F35" s="16" t="n">
+      <c r="F35" s="17" t="n">
         <v>1058000</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="15" t="inlineStr">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t>Hensættelse til udskudt skat</t>
         </is>
       </c>
-      <c r="B36" s="16" t="n">
+      <c r="B36" s="17" t="n">
         <v>48000</v>
       </c>
-      <c r="C36" s="16" t="n">
+      <c r="C36" s="17" t="n">
         <v>131000</v>
       </c>
-      <c r="D36" s="16" t="n">
+      <c r="D36" s="17" t="n">
         <v>99000</v>
       </c>
-      <c r="E36" s="16" t="n">
+      <c r="E36" s="17" t="n">
         <v>77000</v>
       </c>
-      <c r="F36" s="16" t="n">
+      <c r="F36" s="17" t="n">
         <v>70000</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="17" t="inlineStr">
+      <c r="A37" s="15" t="inlineStr">
         <is>
           <t>Hensatte forpligtelser</t>
         </is>
       </c>
-      <c r="B37" s="16" t="n">
+      <c r="B37" s="17" t="n">
         <v>121000</v>
       </c>
-      <c r="C37" s="16" t="n">
+      <c r="C37" s="17" t="n">
         <v>41000</v>
       </c>
-      <c r="D37" s="16" t="n">
+      <c r="D37" s="17" t="n">
         <v>36000</v>
       </c>
-      <c r="E37" s="16" t="n">
+      <c r="E37" s="17" t="n">
         <v>36000</v>
       </c>
-      <c r="F37" s="16" t="n">
+      <c r="F37" s="17" t="n">
         <v>55000</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="15" t="inlineStr">
+      <c r="A38" s="16" t="inlineStr">
         <is>
           <t>Ansvarlig lånekapital (langfristet)</t>
         </is>
       </c>
-      <c r="B38" s="16" t="n"/>
-      <c r="C38" s="16" t="n"/>
-      <c r="D38" s="16" t="n"/>
-      <c r="E38" s="16" t="n"/>
-      <c r="F38" s="16" t="n"/>
+      <c r="B38" s="17" t="n"/>
+      <c r="C38" s="17" t="n"/>
+      <c r="D38" s="17" t="n"/>
+      <c r="E38" s="17" t="n"/>
+      <c r="F38" s="17" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="15" t="inlineStr">
+      <c r="A39" s="16" t="inlineStr">
         <is>
           <t>Langfristede lån</t>
         </is>
       </c>
-      <c r="B39" s="16" t="n">
+      <c r="B39" s="17" t="n">
         <v>190000</v>
       </c>
-      <c r="C39" s="16" t="n"/>
-      <c r="D39" s="16" t="n"/>
-      <c r="E39" s="16" t="n"/>
-      <c r="F39" s="16" t="n"/>
+      <c r="C39" s="17" t="n"/>
+      <c r="D39" s="17" t="n"/>
+      <c r="E39" s="17" t="n"/>
+      <c r="F39" s="17" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="15" t="inlineStr">
+      <c r="A40" s="16" t="inlineStr">
         <is>
           <t>Leasingforpligtelser (langfristet)</t>
         </is>
       </c>
-      <c r="B40" s="16" t="n"/>
-      <c r="C40" s="16" t="n">
+      <c r="B40" s="17" t="n"/>
+      <c r="C40" s="17" t="n">
         <v>138000</v>
       </c>
-      <c r="D40" s="16" t="n">
+      <c r="D40" s="17" t="n">
         <v>129000</v>
       </c>
-      <c r="E40" s="16" t="n">
+      <c r="E40" s="17" t="n">
         <v>105000</v>
       </c>
-      <c r="F40" s="16" t="n">
+      <c r="F40" s="17" t="n">
         <v>95000</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="15" t="inlineStr">
+      <c r="A41" s="16" t="inlineStr">
         <is>
           <t>Anden gæld (langfristet)</t>
         </is>
       </c>
-      <c r="B41" s="16" t="n">
+      <c r="B41" s="17" t="n">
         <v>2000</v>
       </c>
-      <c r="C41" s="16" t="n">
+      <c r="C41" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="D41" s="16" t="n"/>
-      <c r="E41" s="16" t="n"/>
-      <c r="F41" s="16" t="n"/>
+      <c r="D41" s="17" t="n"/>
+      <c r="E41" s="17" t="n"/>
+      <c r="F41" s="17" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="17" t="inlineStr">
+      <c r="A42" s="15" t="inlineStr">
         <is>
           <t>Langfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B42" s="16" t="n">
+      <c r="B42" s="17" t="n">
         <v>192000</v>
       </c>
-      <c r="C42" s="16" t="n">
+      <c r="C42" s="17" t="n">
         <v>770000</v>
       </c>
-      <c r="D42" s="16" t="n">
+      <c r="D42" s="17" t="n">
         <v>901000</v>
       </c>
-      <c r="E42" s="16" t="n">
+      <c r="E42" s="17" t="n">
         <v>1034000</v>
       </c>
-      <c r="F42" s="16" t="n">
+      <c r="F42" s="17" t="n">
         <v>548000</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="15" t="inlineStr">
+      <c r="A43" s="16" t="inlineStr">
         <is>
           <t>Ansvarlig lånekapital (kortfristet)</t>
         </is>
       </c>
-      <c r="B43" s="16" t="n"/>
-      <c r="C43" s="16" t="n"/>
-      <c r="D43" s="16" t="n"/>
-      <c r="E43" s="16" t="n"/>
-      <c r="F43" s="16" t="n"/>
+      <c r="B43" s="17" t="n"/>
+      <c r="C43" s="17" t="n"/>
+      <c r="D43" s="17" t="n"/>
+      <c r="E43" s="17" t="n"/>
+      <c r="F43" s="17" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="15" t="inlineStr">
+      <c r="A44" s="16" t="inlineStr">
         <is>
           <t>Kortfristet del af langfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B44" s="16" t="n">
+      <c r="B44" s="17" t="n">
         <v>9000</v>
       </c>
-      <c r="C44" s="16" t="n"/>
-      <c r="D44" s="16" t="n"/>
-      <c r="E44" s="16" t="n"/>
-      <c r="F44" s="16" t="n"/>
+      <c r="C44" s="17" t="n"/>
+      <c r="D44" s="17" t="n"/>
+      <c r="E44" s="17" t="n"/>
+      <c r="F44" s="17" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="15" t="inlineStr">
+      <c r="A45" s="16" t="inlineStr">
         <is>
           <t>Kreditinstitutter</t>
         </is>
       </c>
-      <c r="B45" s="16" t="n">
+      <c r="B45" s="17" t="n">
         <v>40000</v>
       </c>
-      <c r="C45" s="16" t="n">
+      <c r="C45" s="17" t="n">
         <v>67000</v>
       </c>
-      <c r="D45" s="16" t="n">
+      <c r="D45" s="17" t="n">
         <v>100000</v>
       </c>
-      <c r="E45" s="16" t="n">
+      <c r="E45" s="17" t="n">
         <v>53000</v>
       </c>
-      <c r="F45" s="16" t="n">
+      <c r="F45" s="17" t="n">
         <v>75000</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="15" t="inlineStr">
+      <c r="A46" s="16" t="inlineStr">
         <is>
           <t>Leasingforpligtelser (kortfristet)</t>
         </is>
       </c>
-      <c r="B46" s="16" t="n"/>
-      <c r="C46" s="16" t="n">
+      <c r="B46" s="17" t="n"/>
+      <c r="C46" s="17" t="n">
         <v>38000</v>
       </c>
-      <c r="D46" s="16" t="n">
+      <c r="D46" s="17" t="n">
         <v>36000</v>
       </c>
-      <c r="E46" s="16" t="n">
+      <c r="E46" s="17" t="n">
         <v>35000</v>
       </c>
-      <c r="F46" s="16" t="n">
+      <c r="F46" s="17" t="n">
         <v>34000</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="15" t="inlineStr">
+      <c r="A47" s="16" t="inlineStr">
         <is>
           <t>Leverandører af varer og tjenesteydelser</t>
         </is>
       </c>
-      <c r="B47" s="16" t="n">
+      <c r="B47" s="17" t="n">
         <v>261000</v>
       </c>
-      <c r="C47" s="16" t="n">
+      <c r="C47" s="17" t="n">
         <v>344000</v>
       </c>
-      <c r="D47" s="16" t="n">
+      <c r="D47" s="17" t="n">
         <v>355000</v>
       </c>
-      <c r="E47" s="16" t="n">
+      <c r="E47" s="17" t="n">
         <v>332000</v>
       </c>
-      <c r="F47" s="16" t="n">
+      <c r="F47" s="17" t="n">
         <v>317000</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="15" t="inlineStr">
+      <c r="A48" s="16" t="inlineStr">
         <is>
           <t>Gæld til tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B48" s="16" t="n">
+      <c r="B48" s="17" t="n">
         <v>48000</v>
       </c>
-      <c r="C48" s="16" t="n"/>
-      <c r="D48" s="16" t="n"/>
-      <c r="E48" s="16" t="n"/>
-      <c r="F48" s="16" t="n"/>
+      <c r="C48" s="17" t="n"/>
+      <c r="D48" s="17" t="n"/>
+      <c r="E48" s="17" t="n"/>
+      <c r="F48" s="17" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="15" t="inlineStr">
+      <c r="A49" s="16" t="inlineStr">
         <is>
           <t>Gæld til selskabsdeltagere og ledelse</t>
         </is>
       </c>
-      <c r="B49" s="16" t="n"/>
-      <c r="C49" s="16" t="n"/>
-      <c r="D49" s="16" t="n"/>
-      <c r="E49" s="16" t="n"/>
-      <c r="F49" s="16" t="n"/>
+      <c r="B49" s="17" t="n"/>
+      <c r="C49" s="17" t="n"/>
+      <c r="D49" s="17" t="n"/>
+      <c r="E49" s="17" t="n"/>
+      <c r="F49" s="17" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="15" t="inlineStr">
+      <c r="A50" s="16" t="inlineStr">
         <is>
           <t>Selskabsskat</t>
         </is>
       </c>
-      <c r="B50" s="16" t="n">
+      <c r="B50" s="17" t="n">
         <v>9000</v>
       </c>
-      <c r="C50" s="16" t="n"/>
-      <c r="D50" s="16" t="n"/>
-      <c r="E50" s="16" t="n"/>
-      <c r="F50" s="16" t="n"/>
+      <c r="C50" s="17" t="n"/>
+      <c r="D50" s="17" t="n"/>
+      <c r="E50" s="17" t="n"/>
+      <c r="F50" s="17" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="15" t="inlineStr">
+      <c r="A51" s="16" t="inlineStr">
         <is>
           <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
         </is>
       </c>
-      <c r="B51" s="16" t="n"/>
-      <c r="C51" s="16" t="n"/>
-      <c r="D51" s="16" t="n"/>
-      <c r="E51" s="16" t="n"/>
-      <c r="F51" s="16" t="n"/>
+      <c r="B51" s="17" t="n"/>
+      <c r="C51" s="17" t="n"/>
+      <c r="D51" s="17" t="n"/>
+      <c r="E51" s="17" t="n"/>
+      <c r="F51" s="17" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="15" t="inlineStr">
+      <c r="A52" s="16" t="inlineStr">
         <is>
           <t>Anden gæld (kortfristet)</t>
         </is>
       </c>
-      <c r="B52" s="16" t="n">
+      <c r="B52" s="17" t="n">
         <v>238000</v>
       </c>
-      <c r="C52" s="16" t="n">
+      <c r="C52" s="17" t="n">
         <v>283000</v>
       </c>
-      <c r="D52" s="16" t="n">
+      <c r="D52" s="17" t="n">
         <v>320000</v>
       </c>
-      <c r="E52" s="16" t="n">
+      <c r="E52" s="17" t="n">
         <v>301000</v>
       </c>
-      <c r="F52" s="16" t="n">
+      <c r="F52" s="17" t="n">
         <v>223000</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="15" t="inlineStr">
+      <c r="A53" s="16" t="inlineStr">
         <is>
           <t>Periodeafgrænsningsposter (passiver)</t>
         </is>
       </c>
-      <c r="B53" s="16" t="n">
+      <c r="B53" s="17" t="n">
         <v>6000</v>
       </c>
-      <c r="C53" s="16" t="n"/>
-      <c r="D53" s="16" t="n">
+      <c r="C53" s="17" t="n"/>
+      <c r="D53" s="17" t="n">
         <v>7000</v>
       </c>
-      <c r="E53" s="16" t="n">
+      <c r="E53" s="17" t="n">
         <v>8000</v>
       </c>
-      <c r="F53" s="16" t="n">
+      <c r="F53" s="17" t="n">
         <v>7000</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="17" t="inlineStr">
+      <c r="A54" s="15" t="inlineStr">
         <is>
           <t>Kortfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B54" s="16" t="n">
+      <c r="B54" s="17" t="n">
         <v>611000</v>
       </c>
-      <c r="C54" s="16" t="n">
+      <c r="C54" s="17" t="n">
         <v>825000</v>
       </c>
-      <c r="D54" s="16" t="n">
+      <c r="D54" s="17" t="n">
         <v>927000</v>
       </c>
-      <c r="E54" s="16" t="n">
+      <c r="E54" s="17" t="n">
         <v>837000</v>
       </c>
-      <c r="F54" s="16" t="n">
+      <c r="F54" s="17" t="n">
         <v>716000</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="17" t="inlineStr">
+      <c r="A55" s="15" t="inlineStr">
         <is>
           <t>Gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B55" s="16" t="n">
+      <c r="B55" s="17" t="n">
         <v>924000</v>
       </c>
-      <c r="C55" s="16" t="n">
+      <c r="C55" s="17" t="n">
         <v>1926000</v>
       </c>
-      <c r="D55" s="16" t="n">
+      <c r="D55" s="17" t="n">
         <v>2108000</v>
       </c>
-      <c r="E55" s="16" t="n">
+      <c r="E55" s="17" t="n">
         <v>2108000</v>
       </c>
-      <c r="F55" s="16" t="n">
+      <c r="F55" s="17" t="n">
         <v>1506000</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="17" t="inlineStr">
+      <c r="A56" s="15" t="inlineStr">
         <is>
           <t>Passiver</t>
         </is>
       </c>
-      <c r="B56" s="16" t="n">
+      <c r="B56" s="17" t="n">
         <v>1410000</v>
       </c>
-      <c r="C56" s="16" t="n">
+      <c r="C56" s="17" t="n">
         <v>2496000</v>
       </c>
-      <c r="D56" s="16" t="n">
+      <c r="D56" s="17" t="n">
         <v>2655000</v>
       </c>
-      <c r="E56" s="16" t="n">
+      <c r="E56" s="17" t="n">
         <v>2667000</v>
       </c>
-      <c r="F56" s="16" t="n">
+      <c r="F56" s="17" t="n">
         <v>2631000</v>
       </c>
     </row>
@@ -5985,6 +6128,130 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="72" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Pengestrømsopgørelse (t.EUR)</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C1" s="3" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D1" s="3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E1" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F1" s="3" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="n">
+        <v>171000</v>
+      </c>
+      <c r="C2" s="17" t="n">
+        <v>72000</v>
+      </c>
+      <c r="D2" s="17" t="n">
+        <v>72000</v>
+      </c>
+      <c r="E2" s="17" t="n">
+        <v>127000</v>
+      </c>
+      <c r="F2" s="17" t="n">
+        <v>225000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="n">
+        <v>-65000</v>
+      </c>
+      <c r="C3" s="17" t="n">
+        <v>-601000</v>
+      </c>
+      <c r="D3" s="17" t="n">
+        <v>-136000</v>
+      </c>
+      <c r="E3" s="17" t="n">
+        <v>-98000</v>
+      </c>
+      <c r="F3" s="17" t="n">
+        <v>-86000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="n">
+        <v>53000</v>
+      </c>
+      <c r="C4" s="17" t="n">
+        <v>435000</v>
+      </c>
+      <c r="D4" s="17" t="n">
+        <v>79000</v>
+      </c>
+      <c r="E4" s="17" t="n">
+        <v>12000</v>
+      </c>
+      <c r="F4" s="17" t="n">
+        <v>-135000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="n"/>
+      <c r="C5" s="17" t="n">
+        <v>-94000</v>
+      </c>
+      <c r="D5" s="17" t="n"/>
+      <c r="E5" s="17" t="n"/>
+      <c r="F5" s="17" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7183,7 +7450,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
